--- a/config/trainer/trainer_level.xlsx
+++ b/config/trainer/trainer_level.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="trainer_level" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="trainer_level" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>冒険の証I</t>
+          <t>冒险的证明I</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1292,7 +1292,6 @@
           <t>{gold=20000;11=10}</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1302,7 +1301,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>冒険の証II</t>
+          <t>冒险之证II</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1350,7 +1349,6 @@
           <t>{gold=24750;11=20}</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1360,7 +1358,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>冒険の証III</t>
+          <t>冒险之证III</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1408,7 +1406,6 @@
           <t>{gold=30000;11=30}</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1418,7 +1415,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>冒険の証IV</t>
+          <t>冒险之证IV</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1466,7 +1463,6 @@
           <t>{gold=35750;12=13}</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1476,7 +1472,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>冒険の証V</t>
+          <t>冒险的证明V</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1524,7 +1520,6 @@
           <t>{gold=42000;12=16}</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1534,7 +1529,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>冒険の証VI</t>
+          <t>冒险的证明VI</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1582,7 +1577,6 @@
           <t>{gold=48750;12=20}</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1592,7 +1586,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>冒険の証VII</t>
+          <t>冒险的证明VII</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1640,7 +1634,6 @@
           <t>{gold=56000;13=7}</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1650,7 +1643,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>冒険の証VIII</t>
+          <t>冒险之证VIII</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1698,7 +1691,6 @@
           <t>{gold=63750;13=8}</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1708,7 +1700,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>冒険の証IX</t>
+          <t>冒险的证明IX</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1756,7 +1748,6 @@
           <t>{gold=72000;13=9}</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1766,7 +1757,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>冒険の証X</t>
+          <t>冒险的证明X</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1828,7 +1819,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>冒険の証XI</t>
+          <t>冒险的证明XI</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1890,7 +1881,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>冒険の証XII</t>
+          <t>冒险的证明XII</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
